--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488210_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488210_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.961</v>
+        <v>6.7576</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9824</v>
+        <v>4.4835</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9786</v>
+        <v>2.2741</v>
       </c>
       <c r="G2" t="n">
         <v>6.1099</v>
@@ -610,13 +610,13 @@
         <v>2.4087</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7952</v>
+        <v>-0.9986</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7996</v>
+        <v>-0.2984</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9956</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>2.2022</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0615</v>
+        <v>4.2857</v>
       </c>
       <c r="E3" t="n">
-        <v>3.555</v>
+        <v>3.4685</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5066</v>
+        <v>0.8172</v>
       </c>
       <c r="G3" t="n">
         <v>0.9540999999999999</v>
@@ -688,13 +688,13 @@
         <v>2.0382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6807</v>
+        <v>-0.0951</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1131</v>
+        <v>-0.1996</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7938</v>
+        <v>0.1044</v>
       </c>
       <c r="V3" t="n">
         <v>1.5738</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2421</v>
+        <v>3.7513</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8965</v>
+        <v>1.6027</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3456</v>
+        <v>2.1486</v>
       </c>
       <c r="G4" t="n">
         <v>1.2965</v>
@@ -766,13 +766,13 @@
         <v>3.5205</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6287</v>
+        <v>-1.1195</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5844</v>
+        <v>-0.8782</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0443</v>
+        <v>-0.2413</v>
       </c>
       <c r="V4" t="n">
         <v>2.8332</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2484</v>
+        <v>2.3764</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5848</v>
+        <v>1.7374</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6636</v>
+        <v>0.639</v>
       </c>
       <c r="G5" t="n">
         <v>4.3502</v>
@@ -844,13 +844,13 @@
         <v>1.4823</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6021</v>
+        <v>-0.4741</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4713</v>
+        <v>-0.3186</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1308</v>
+        <v>-0.1555</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9439</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1363</v>
+        <v>0.1177</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0159</v>
+        <v>-0.0273</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1204</v>
+        <v>0.145</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6957</v>
@@ -1000,13 +1000,13 @@
         <v>0.7411</v>
       </c>
       <c r="S7" t="n">
-        <v>0.147</v>
+        <v>0.1284</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3246</v>
+        <v>0.2814</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1776</v>
+        <v>-0.153</v>
       </c>
       <c r="V7" t="n">
         <v>0.9439</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5292</v>
+        <v>-0.0515</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8749</v>
+        <v>-1.5696</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3457</v>
+        <v>1.518</v>
       </c>
       <c r="G8" t="n">
         <v>-2.3071</v>
@@ -1078,13 +1078,13 @@
         <v>2.9646</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3338</v>
+        <v>-0.8562</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.909</v>
+        <v>-0.6037</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4248</v>
+        <v>-0.2525</v>
       </c>
       <c r="V8" t="n">
         <v>1.2589</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.684</v>
+        <v>-0.8874</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3214</v>
+        <v>-0.8203</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3626</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>1.6822</v>
@@ -1156,13 +1156,13 @@
         <v>2.0382</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0899</v>
+        <v>-1.2933</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8207</v>
+        <v>-0.3196</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2692</v>
+        <v>-0.9737</v>
       </c>
       <c r="V9" t="n">
         <v>-2.2027</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.13</v>
+        <v>-1.9089</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0268</v>
+        <v>0.0712</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1032</v>
+        <v>-1.9801</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3863</v>
@@ -1234,13 +1234,13 @@
         <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7262</v>
+        <v>-0.5052</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6019</v>
+        <v>-0.5039</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1244</v>
+        <v>-0.0012</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5733</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5135</v>
+        <v>-4.101</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2257</v>
+        <v>-2.8133</v>
       </c>
       <c r="F11" t="n">
         <v>-1.2878</v>
@@ -1312,10 +1312,10 @@
         <v>2.7793</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2611</v>
+        <v>-0.3264</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2326</v>
+        <v>-0.355</v>
       </c>
       <c r="U11" t="n">
         <v>0.0286</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.025</v>
+        <v>12.5723</v>
       </c>
       <c r="E12" t="n">
-        <v>7.818199999999999</v>
+        <v>8.3652</v>
       </c>
       <c r="F12" t="n">
-        <v>4.206899999999999</v>
+        <v>4.2069</v>
       </c>
       <c r="G12" t="n">
         <v>13.8136</v>
@@ -1390,10 +1390,10 @@
         <v>19.4552</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.0871</v>
+        <v>-5.539999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.7428</v>
+        <v>-3.1956</v>
       </c>
       <c r="U12" t="n">
         <v>-2.3443</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.7475</v>
+        <v>3.4903</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2505</v>
+        <v>2.8381</v>
       </c>
       <c r="F13" t="n">
-        <v>0.497</v>
+        <v>0.6522</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6207</v>
@@ -1468,13 +1468,13 @@
         <v>1.4823</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5942</v>
+        <v>0.1486</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7784</v>
+        <v>-0.1909</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1843</v>
+        <v>0.3395</v>
       </c>
       <c r="V13" t="n">
         <v>4.4065</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2579</v>
+        <v>2.2584</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3567</v>
+        <v>2.2588</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0989</v>
+        <v>-0.0004</v>
       </c>
       <c r="G14" t="n">
         <v>-1.8579</v>
@@ -1546,13 +1546,13 @@
         <v>2.594</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7272</v>
+        <v>0.7278</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3084</v>
+        <v>0.2105</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4188</v>
+        <v>0.5173</v>
       </c>
       <c r="V14" t="n">
         <v>2.8327</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. HEPBURN</t>
+          <t>A. GALLEGO GÓMEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6156</v>
+        <v>0.3221</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7502</v>
+        <v>0.3221</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1347</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2293</v>
+        <v>0.3221</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0174</v>
+        <v>0.3221</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2119</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7845</v>
+        <v>0.3221</v>
       </c>
       <c r="K15" t="n">
-        <v>2.121</v>
+        <v>0.3221</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6635</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.0138</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.1384</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8754</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.297</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9646</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7719</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2459</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.526</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. GALLEGO GÓMEZ</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3221</v>
+        <v>-0.3299</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3221</v>
+        <v>0.9171</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-1.247</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3221</v>
+        <v>-0.4856</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3221</v>
+        <v>0.5635</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-1.0491</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3221</v>
+        <v>0.4192</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3221</v>
+        <v>1.0306</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-0.9048</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.4671</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.4377</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.1834</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.0833</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>K. DELGADO YEBOAH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2079</v>
+        <v>-0.5573</v>
       </c>
       <c r="E17" t="n">
-        <v>1.113</v>
+        <v>1.4271</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3209</v>
+        <v>-1.9844</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4856</v>
+        <v>-0.3291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5635</v>
+        <v>-0.3041</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0491</v>
+        <v>-0.025</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4192</v>
+        <v>1.9073</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0306</v>
+        <v>2.5162</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.6089</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9048</v>
+        <v>-2.2364</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4671</v>
+        <v>-2.8203</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4377</v>
+        <v>0.5839</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3706</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.891</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3706</v>
+        <v>2.2234</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2221</v>
+        <v>1.4394</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3793</v>
+        <v>0.2643</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1572</v>
+        <v>1.1751</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3144</v>
+        <v>3.1466</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6294</v>
+        <v>-3.1466</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9159</v>
+        <v>-0.8185</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8502</v>
+        <v>-0.6544</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.1641</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0144</v>
@@ -1858,13 +1858,13 @@
         <v>0.1853</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0868</v>
+        <v>0.0106</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2189</v>
+        <v>-0.023</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1321</v>
+        <v>0.0336</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. KOZAR SIMIONIKA</t>
+          <t>P. HEPBURN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3322</v>
+        <v>-0.8534</v>
       </c>
       <c r="E19" t="n">
-        <v>0.995</v>
+        <v>0.2813</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3271</v>
+        <v>-1.1347</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5797</v>
+        <v>-0.2293</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8409</v>
+        <v>-0.0174</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2611</v>
+        <v>-0.2119</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5884</v>
+        <v>2.7845</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5884</v>
+        <v>2.121</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.6635</v>
       </c>
       <c r="M19" t="n">
-        <v>0.008699999999999999</v>
+        <v>-3.0138</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2524</v>
+        <v>-2.1384</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2611</v>
+        <v>-0.8754</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.297</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9646</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5059</v>
+        <v>1.3029</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3246</v>
+        <v>0.7769</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1813</v>
+        <v>0.526</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2583</v>
+        <v>-0.63</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2589</v>
+        <v>-0.3155</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.5172</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. DELGADO YEBOAH</t>
+          <t>M. KOZAR SIMIONIKA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0342</v>
+        <v>-1.4547</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0561</v>
+        <v>0.897</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0904</v>
+        <v>-2.3518</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3291</v>
+        <v>-0.5797</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3041</v>
+        <v>-0.8409</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.025</v>
+        <v>0.2611</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9073</v>
+        <v>-0.5884</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5162</v>
+        <v>-0.5884</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6089</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2364</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.8203</v>
+        <v>-0.2524</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5839</v>
+        <v>0.2611</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6676</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.891</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2234</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0376</v>
+        <v>0.3833</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1067</v>
+        <v>0.2266</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0692</v>
+        <v>0.1567</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.2583</v>
       </c>
       <c r="W20" t="n">
-        <v>3.1466</v>
+        <v>1.2589</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.1466</v>
+        <v>-2.5172</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. GARCIA FERNANDEZ</t>
+          <t>V. PIETUKHOV</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5507</v>
+        <v>-2.4257</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3999</v>
+        <v>-1.8813</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1508</v>
+        <v>-0.5444</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9776</v>
+        <v>-1.3093</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2435</v>
+        <v>-1.0359</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7342</v>
+        <v>-0.2735</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8254</v>
+        <v>-0.0362</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2315</v>
+        <v>-0.2234</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.0569</v>
+        <v>0.1872</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1522</v>
+        <v>-1.2731</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.475</v>
+        <v>-0.8124</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3227</v>
+        <v>-0.4607</v>
       </c>
       <c r="P21" t="n">
-        <v>1.297</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1117</v>
+        <v>-2.0382</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4087</v>
+        <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>1.6482</v>
+        <v>0.7539</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7971</v>
+        <v>0.1931</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8511</v>
+        <v>0.5608</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.5183</v>
+        <v>-0.9439</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.26</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2583</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. FAJANA</t>
+          <t>M. GARCIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6761</v>
+        <v>-2.7878</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6546</v>
+        <v>-2.6937</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9785</v>
+        <v>-0.0941</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.593</v>
+        <v>-2.9776</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.8156</v>
+        <v>-2.2435</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2226</v>
+        <v>-0.7342</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3814</v>
+        <v>-0.8254</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.8436</v>
+        <v>0.2315</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4622</v>
+        <v>-1.0569</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2115</v>
+        <v>-2.1522</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.972</v>
+        <v>-2.475</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7604</v>
+        <v>0.3227</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.594</v>
+        <v>1.297</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.7057</v>
+        <v>-1.1117</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1117</v>
+        <v>2.4087</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8248</v>
+        <v>1.4111</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4326</v>
+        <v>0.5034</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3922</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3139</v>
+        <v>-2.5183</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-1.26</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3139</v>
+        <v>-1.2583</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. PIETUKHOV</t>
+          <t>O. FAJANA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0866</v>
+        <v>-3.5987</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5668</v>
+        <v>-4.6339</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5198</v>
+        <v>1.0352</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3093</v>
+        <v>-1.593</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0359</v>
+        <v>-3.8156</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2735</v>
+        <v>2.2226</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0362</v>
+        <v>-1.3814</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2234</v>
+        <v>-2.8436</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1872</v>
+        <v>1.4622</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2731</v>
+        <v>-0.2115</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8124</v>
+        <v>-0.972</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4607</v>
+        <v>0.7604</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9264</v>
+        <v>-2.594</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0382</v>
+        <v>-3.7057</v>
       </c>
       <c r="R23" t="n">
         <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>0.093</v>
+        <v>0.9022</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4924</v>
+        <v>0.4533</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5854</v>
+        <v>0.4489</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9439</v>
+        <v>-0.3139</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.9439</v>
+        <v>-0.3139</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1645</v>
+        <v>-4.617</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.579</v>
+        <v>-3.2852</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5855</v>
+        <v>-1.3318</v>
       </c>
       <c r="G24" t="n">
         <v>-2.139</v>
@@ -2326,13 +2326,13 @@
         <v>0.7411</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9874000000000001</v>
+        <v>-0.4399</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5471</v>
+        <v>-0.2534</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4402</v>
+        <v>-0.1865</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.025</v>
+        <v>-11.3722</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.206899999999999</v>
+        <v>-4.206999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.8182</v>
+        <v>-7.1653</v>
       </c>
       <c r="G25" t="n">
         <v>-13.8135</v>
@@ -2383,7 +2383,7 @@
         <v>2.393599999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5010000000000003</v>
+        <v>-0.5010000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-15.706</v>
@@ -2404,16 +2404,16 @@
         <v>13.8964</v>
       </c>
       <c r="S25" t="n">
-        <v>6.0871</v>
+        <v>6.739999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3444</v>
+        <v>2.3442</v>
       </c>
       <c r="U25" t="n">
-        <v>3.742999999999999</v>
+        <v>4.395900000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>1.259800000000001</v>
+        <v>1.2598</v>
       </c>
       <c r="W25" t="n">
         <v>11.0114</v>
